--- a/GPIpuget/project/Pre Verilog Run Checks.xlsx
+++ b/GPIpuget/project/Pre Verilog Run Checks.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="30">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -51,10 +51,7 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>PEBBLEtiehi.bio</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.v</t>
+    <t>No missing bio or symbol files...</t>
   </si>
   <si>
     <t>Missing Nets</t>
@@ -491,6 +488,26 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -504,34 +521,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -546,15 +543,35 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -566,47 +583,27 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -641,7 +638,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -659,24 +656,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -686,37 +678,37 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -726,22 +718,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -751,22 +743,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -776,22 +768,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -801,24 +793,24 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>1</v>

--- a/GPIpuget/project/Pre Verilog Run Checks.xlsx
+++ b/GPIpuget/project/Pre Verilog Run Checks.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="31">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -51,7 +51,10 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>No missing bio or symbol files...</t>
+    <t>PEBBLEtiehi.bio</t>
+  </si>
+  <si>
+    <t>PEBBLEtiehi.v</t>
   </si>
   <si>
     <t>Missing Nets</t>
@@ -488,7 +491,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -508,7 +511,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -528,7 +531,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -543,7 +546,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -558,7 +561,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -578,14 +581,14 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
     </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -598,12 +601,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -638,7 +641,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -656,6 +659,11 @@
         <v>7</v>
       </c>
     </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -668,7 +676,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -678,22 +686,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -708,7 +716,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -718,7 +726,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -733,7 +741,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -743,7 +751,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -758,7 +766,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -768,7 +776,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -783,7 +791,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -793,7 +801,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -808,7 +816,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Pre Verilog Run Checks.xlsx
+++ b/GPIpuget/project/Pre Verilog Run Checks.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="30">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -36,10 +36,10 @@
     <t>0</t>
   </si>
   <si>
-    <t>Overview</t>
-  </si>
-  <si>
-    <t>Your schematic contains no net zero.</t>
+    <t>XGPI,XMAIN</t>
+  </si>
+  <si>
+    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
   </si>
   <si>
     <t>Validate no "text" in Datamaps</t>
@@ -61,9 +61,6 @@
   </si>
   <si>
     <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -491,6 +488,26 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -504,34 +521,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -546,15 +543,35 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -566,47 +583,27 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -691,32 +688,32 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -726,22 +723,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -751,22 +748,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -776,22 +773,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -801,24 +798,24 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>1</v>

--- a/GPIpuget/project/Pre Verilog Run Checks.xlsx
+++ b/GPIpuget/project/Pre Verilog Run Checks.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="30">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -36,31 +36,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Your schematic contains no net zero.</t>
+  </si>
+  <si>
+    <t>Validate no "text" in Datamaps</t>
+  </si>
+  <si>
+    <t>No errors</t>
+  </si>
+  <si>
+    <t>Missing Bio Symbol Files</t>
+  </si>
+  <si>
+    <t>No missing bio or symbol files...</t>
+  </si>
+  <si>
+    <t>Missing Nets</t>
+  </si>
+  <si>
+    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
+  </si>
+  <si>
     <t>XGPI,XMAIN</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
-  </si>
-  <si>
-    <t>Validate no "text" in Datamaps</t>
-  </si>
-  <si>
-    <t>No errors</t>
-  </si>
-  <si>
-    <t>Missing Bio Symbol Files</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.bio</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.v</t>
-  </si>
-  <si>
-    <t>Missing Nets</t>
-  </si>
-  <si>
-    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -638,7 +638,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -656,24 +656,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -683,12 +678,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">

--- a/GPIpuget/project/Pre Verilog Run Checks.xlsx
+++ b/GPIpuget/project/Pre Verilog Run Checks.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="32">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -61,6 +61,12 @@
   </si>
   <si>
     <t>XGPI,XMAIN</t>
+  </si>
+  <si>
+    <t>XU6,trim_vbuffer_negative</t>
+  </si>
+  <si>
+    <t>XU6,trim_vbuffer_positive</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -488,7 +494,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -508,7 +514,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -528,7 +534,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -543,7 +549,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -558,7 +564,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -578,12 +584,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -598,12 +604,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -663,7 +669,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -696,37 +702,22 @@
         <v>12</v>
       </c>
     </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -751,7 +742,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -776,7 +767,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -801,6 +792,31 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
@@ -808,7 +824,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Pre Verilog Run Checks.xlsx
+++ b/GPIpuget/project/Pre Verilog Run Checks.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="29">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -36,10 +36,10 @@
     <t>0</t>
   </si>
   <si>
-    <t>Overview</t>
-  </si>
-  <si>
-    <t>Your schematic contains no net zero.</t>
+    <t>XGPI,XMAIN</t>
+  </si>
+  <si>
+    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
   </si>
   <si>
     <t>Validate no "text" in Datamaps</t>
@@ -58,15 +58,6 @@
   </si>
   <si>
     <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN</t>
-  </si>
-  <si>
-    <t>XU6,trim_vbuffer_negative</t>
-  </si>
-  <si>
-    <t>XU6,trim_vbuffer_positive</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -494,7 +485,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -514,7 +505,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -534,7 +525,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -549,6 +540,46 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
     </row>
@@ -557,7 +588,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -569,47 +600,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +660,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -689,42 +680,32 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -734,7 +715,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -749,7 +730,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -759,7 +740,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -774,7 +755,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -784,7 +765,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -799,7 +780,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -809,7 +790,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -824,7 +805,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Pre Verilog Run Checks.xlsx
+++ b/GPIpuget/project/Pre Verilog Run Checks.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="30">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -36,28 +36,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Your schematic contains no net zero.</t>
+  </si>
+  <si>
+    <t>Validate no "text" in Datamaps</t>
+  </si>
+  <si>
+    <t>No errors</t>
+  </si>
+  <si>
+    <t>Missing Bio Symbol Files</t>
+  </si>
+  <si>
+    <t>No missing bio or symbol files...</t>
+  </si>
+  <si>
+    <t>Missing Nets</t>
+  </si>
+  <si>
+    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
+  </si>
+  <si>
     <t>XGPI,XMAIN</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
-  </si>
-  <si>
-    <t>Validate no "text" in Datamaps</t>
-  </si>
-  <si>
-    <t>No errors</t>
-  </si>
-  <si>
-    <t>Missing Bio Symbol Files</t>
-  </si>
-  <si>
-    <t>No missing bio or symbol files...</t>
-  </si>
-  <si>
-    <t>Missing Nets</t>
-  </si>
-  <si>
-    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -485,7 +488,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -505,7 +508,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -525,7 +528,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -540,7 +543,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -555,7 +558,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -575,14 +578,14 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
     </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -595,12 +598,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -680,17 +683,17 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -705,7 +708,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -715,7 +718,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -730,7 +733,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -740,7 +743,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -755,7 +758,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -765,7 +768,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -780,7 +783,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -790,7 +793,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -805,7 +808,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">
